--- a/原始資料/一梅花被插叫.xlsx
+++ b/原始資料/一梅花被插叫.xlsx
@@ -8,10 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="被插叫說明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14.LHO賭倍後" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15.LHO一階插叫後" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16.LHO二階插叫後" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17.三情況對照" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15.LHO賭倍後" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16.LHO一階插叫後" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17.LHO二階插叫後" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18.三情況對照" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -124,16 +124,16 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -532,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -568,266 +568,278 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
+          <t>★ 家規點力</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>本檔採用家規點力：1♣ 開叫下修為 15 點以上，**所有答叫點力上修 1 點**。本表全部叫品都是對 1♣ 的應叫，因此整份表的點力一律 +1（原書數值 = 表列值 -1）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
           <t>本表涵蓋什麼</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>**開叫 1♣ 之後，左手敵家（L.H.O.）出手干擾**時，應叫者該怎麼叫。
 三種干擾形式各一張表：賭倍／一階插叫／二階插叫。</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>★ 來源不同</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>這份圖使用的是**台港術語**（賭倍、示叫、敵叫組、擋），與資料夾裡《北歐接力精確體系》那本書的簡體術語（加倍、扣叫、花色套、止張）是兩套不同的說法，體系設計也不同。兩者請勿混用——本檔獨立存在，沒有接進網站。</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr"/>
-      <c r="B7" s="5" t="inlineStr"/>
-    </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr"/>
+      <c r="B8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>術語對照</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>說明</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>L.H.O.</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Left Hand Opponent，開叫人左手邊的敵家，也就是在應叫者之前先發言的那一位。</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>賭倍 / 再賭倍</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Double／Redouble。</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>示叫敵叫組</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Cuebid，直接叫出敵方叫過的那門花色。</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>敵叫組</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>敵方插叫的那門花色。</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>擋 / 擋張</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Stopper，該門花色有牽制敵方的大牌。</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>牌組</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>花色套。「5 張以上的牌組」＝5 張以上的一門花色。</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>三門牌組</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>Three-suiter，三門花色都有長度（對應敵叫組短門）。</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr"/>
-      <c r="B16" s="5" t="inlineStr"/>
-    </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr"/>
+      <c r="B17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>★ 三張表看出來的規律</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>說明</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>賭倍反而多給你一格</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>未受干擾時 1♦ 是 0-7 點一整段。但**敵方賭倍之後**，PASS 和 1♦ 把它切成兩段：PASS = 0-3、1♦ = 4-7。多出來的那個叫品（PASS）讓你能先分弱牌強度。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>「有擋」的無將往上搬一階</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>一階插叫後用 **1NT** 表示「敵叫組有擋、8-10 點」；二階插叫後同樣的意思改用 **2NT**。點力範圍一模一樣，只是被敵方的階數推高一階。</t>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>未受干擾時 1♦ 是 0-8 點一整段。但**敵方賭倍之後**，PASS 和 1♦ 把它切成兩段：PASS = 0-3、1♦ = 4-7。多出來的那個叫品（PASS）讓你能先分弱牌強度。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
+          <t>「有擋」的無將往上搬一階</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>一階插叫後用 **1NT** 表示「敵叫組有擋、9-11 點」；二階插叫後同樣的意思改用 **2NT**。點力範圍一模一樣，只是被敵方的階數推高一階。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
           <t>★ 平均牌型階梯被壓縮</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>一階插叫後有三級：1NT(8-10) → 2NT(11-13) → 3NT(14-15)。
 二階插叫後只剩兩級：2NT(8-10) → 3NT(11-13)。
-**14-15 點的平均牌型在二階插叫後沒有專屬叫品**——空間被敵方吃掉了。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+**15-16 點的平均牌型在二階插叫後沒有專屬叫品**——空間被敵方吃掉了。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>示叫在二階多了牌型保證</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>一階插叫後的示叫只要求「8點以上、敵叫組無擋、無 5 張牌組」。
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>一階插叫後的示叫只要求「9點以上、敵叫組無擋、無 5 張牌組」。
 二階插叫後則加上牌型保證：敵叫組是高花 → 保證另一門高花有 4 張；敵叫組是低花 → 保證兩門高花至少 4-3。</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>點力門檻隨階數放寬</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>PASS 的上限：賭倍時 0-3 → 一階 0-3（或 4 點而無 A/K）→ 二階 0-4（或 5-6 無可叫牌組）。敵方叫得越高，你越容易被迫 PASS。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr"/>
-      <c r="B23" s="5" t="inlineStr"/>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>PASS 的上限：賭倍時 0-4 → 一階 0-4（或 5 點而無 A/K）→ 二階 0-5（或 6-7 無可叫牌組）。敵方叫得越高，你越容易被迫 PASS。</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr"/>
+      <c r="B24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>工作表</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>內容</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>2. LHO賭倍後</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>敵方賭倍時應叫者的五種處理。</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>3. LHO一階插叫後</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>敵方一階插叫時應叫者的十種處理。</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>4. LHO二階插叫後</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>敵方二階插叫時應叫者的七種處理。</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>5. 三情況對照</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>同一類叫品在三種干擾下的差異，橫向對照。</t>
         </is>
@@ -900,7 +912,7 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>0-3 點</t>
+          <t>0-4 點</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
@@ -918,7 +930,7 @@
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>4-7 點</t>
+          <t>5-8 點</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
@@ -936,7 +948,7 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>8 點以上</t>
+          <t>9 點以上</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -958,7 +970,7 @@
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>4-7 點</t>
+          <t>5-8 點</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
@@ -1004,7 +1016,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>1NT 在這裡不是無將傾向，而是**雙低花 5-5 以上的牌型叫**，點力只有 4-7——與一階／二階插叫後的 1NT／2NT 意義完全不同。</t>
+          <t>1NT 在這裡不是無將傾向，而是**雙低花 5-5 以上的牌型叫**，點力只有 5-8——與一階／二階插叫後的 1NT／2NT 意義完全不同。</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1090,7 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>0-3 點，或 4 點而無 A 或 K</t>
+          <t>0-4 點，或 5 點而無 A 或 K</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
@@ -1096,7 +1108,7 @@
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>4-7 點</t>
+          <t>5-8 點</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
@@ -1114,7 +1126,7 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>4-7 點</t>
+          <t>5-8 點</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -1132,7 +1144,7 @@
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>如是平均牌型一定是 8-10 點</t>
+          <t>如是平均牌型一定是 9-11 點</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
@@ -1150,7 +1162,7 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>5-7 點</t>
+          <t>6-8 點</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -1168,7 +1180,7 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>8 點以上</t>
+          <t>9 點以上</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
@@ -1190,7 +1202,7 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>8 點以上</t>
+          <t>9 點以上</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
@@ -1208,7 +1220,7 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>11-13 點</t>
+          <t>12-14 點</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
@@ -1226,7 +1238,7 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>14-15 點</t>
+          <t>15-16 點</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
@@ -1244,7 +1256,7 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>8 點以上</t>
+          <t>9 點以上</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
@@ -1264,7 +1276,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>「跳叫一門花色」與「1NT」的取捨：兩者都是 8 點以上，差別在敵叫組有沒有擋——有擋優先叫 1NT。</t>
+          <t>「跳叫一門花色」與「1NT」的取捨：兩者都是 9 點以上，差別在敵叫組有沒有擋——有擋優先叫 1NT。</t>
         </is>
       </c>
     </row>
@@ -1346,12 +1358,12 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>0-4 點（任何牌型），或 5-6 點</t>
+          <t>0-5 點（任何牌型），或 6-7 點</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>5-6 點時須無可叫牌組</t>
+          <t>6-7 點時須無可叫牌組</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr"/>
@@ -1364,7 +1376,7 @@
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>6-7 點，或 8-12 點</t>
+          <t>7-8 點，或 9-13 點</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
@@ -1382,7 +1394,7 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>4-6 點</t>
+          <t>5-7 點</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -1400,7 +1412,7 @@
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>8 點以上</t>
+          <t>9 點以上</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
@@ -1418,7 +1430,7 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>如為平均牌型是 8-10 點</t>
+          <t>如為平均牌型是 9-11 點</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -1436,7 +1448,7 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>11-13 點</t>
+          <t>12-14 點</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
@@ -1454,7 +1466,7 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>8 點以上</t>
+          <t>9 點以上</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
@@ -1468,14 +1480,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>★ 平均牌型只剩兩級：2NT(8-10) → 3NT(11-13)。**14-15 點的平均牌型沒有專屬叫品**，空間被敵方的二階插叫吃掉了。</t>
+          <t>★ 平均牌型只剩兩級：2NT(9-11) → 3NT(12-14)。**15-16 點的平均牌型沒有專屬叫品**，空間被敵方的二階插叫吃掉了。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>★ 賭倍的點力被切成兩段（6-7 或 8-12），兩段都是「無可叫牌組」——開叫人必須靠後續叫牌才能分辨是哪一段。</t>
+          <t>★ 賭倍的點力被切成兩段（7-8 或 9-13），兩段都是「無可叫牌組」——開叫人必須靠後續叫牌才能分辨是哪一段。</t>
         </is>
       </c>
     </row>
@@ -1557,17 +1569,17 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>0-3 點</t>
+          <t>0-4 點</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>0-3 點，或 4 點而無 A 或 K</t>
+          <t>0-4 點，或 5 點而無 A 或 K</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>0-4 點任何牌型，或 5-6 點但無可叫牌組</t>
+          <t>0-5 點任何牌型，或 6-7 點但無可叫牌組</t>
         </is>
       </c>
     </row>
@@ -1579,17 +1591,17 @@
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>再賭倍 ＝ 8 點以上的平均牌型</t>
+          <t>再賭倍 ＝ 9 點以上的平均牌型</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>賭倍 ＝ 4-7 點，無 5 張高花或無 5 張好低花</t>
+          <t>賭倍 ＝ 5-8 點，無 5 張高花或無 5 張好低花</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>賭倍 ＝ 6-7 點 或 8-12 點，無可叫牌組</t>
+          <t>賭倍 ＝ 7-8 點 或 9-13 點，無可叫牌組</t>
         </is>
       </c>
     </row>
@@ -1601,17 +1613,17 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>1♦ ＝ 4-7 點</t>
+          <t>1♦ ＝ 5-8 點</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>一階花色 ＝ 4-7 點，5 張以上牌組</t>
+          <t>一階花色 ＝ 5-8 點，5 張以上牌組</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>二階花色 ＝ 4-6 點，5 張以上牌組</t>
+          <t>二階花色 ＝ 5-7 點，5 張以上牌組</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1640,12 @@
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>簡單叫出二階高花 ＝ 5-7 點，5 張以上牌組</t>
+          <t>簡單叫出二階高花 ＝ 6-8 點，5 張以上牌組</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>三階花色 ＝ 8 點以上，5 張以上牌組</t>
+          <t>三階花色 ＝ 9 點以上，5 張以上牌組</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1662,7 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>8 點以上，5 張以上牌組（敵叫組通常無擋）</t>
+          <t>9 點以上，5 張以上牌組（敵叫組通常無擋）</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
@@ -1667,13 +1679,13 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>4-7 點，兩門低花 5-5 以上
+          <t>5-8 點，兩門低花 5-5 以上
 （牌型叫，非無將傾向）</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>敵叫組有擋；平均牌型時 8-10 點</t>
+          <t>敵叫組有擋；平均牌型時 9-11 點</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
@@ -1695,12 +1707,12 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>平均牌型，11-13 點，敵叫組有擋</t>
+          <t>平均牌型，12-14 點，敵叫組有擋</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>敵叫組有擋；平均牌型時 8-10 點</t>
+          <t>敵叫組有擋；平均牌型時 9-11 點</t>
         </is>
       </c>
     </row>
@@ -1717,24 +1729,24 @@
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>平均牌型，14-15 點，敵叫組有良好擋張</t>
+          <t>平均牌型，15-16 點，敵叫組有良好擋張</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>11-13 點平均牌型，敵叫組有良好擋張</t>
+          <t>12-14 點平均牌型，敵叫組有良好擋張</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="17" t="inlineStr">
         <is>
-          <t>14-15 點平均牌型</t>
+          <t>15-16 點平均牌型</t>
         </is>
       </c>
       <c r="B12" s="18" t="inlineStr">
         <is>
-          <t>再賭倍（8 點以上平均牌型都走這裡）</t>
+          <t>再賭倍（9 點以上平均牌型都走這裡）</t>
         </is>
       </c>
       <c r="C12" s="18" t="inlineStr">
@@ -1761,12 +1773,12 @@
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>8 點以上，敵叫組無擋，且無 5 張牌組</t>
+          <t>9 點以上，敵叫組無擋，且無 5 張牌組</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>8 點以上；敵叫組是高花→另一門高花 4 張，敵叫組是低花→兩門高花至少 4-3</t>
+          <t>9 點以上；敵叫組是高花→另一門高花 4 張，敵叫組是低花→兩門高花至少 4-3</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1795,7 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>8 點以上的三門牌組，敵叫組短門</t>
+          <t>9 點以上的三門牌組，敵叫組短門</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
@@ -1824,7 +1836,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>★ 黃底那一列是三種干擾下最明顯的落差：一階插叫後 14-15 點平均牌型有 3NT 可叫，二階插叫後就沒有對應叫品了。</t>
+          <t>★ 黃底那一列是三種干擾下最明顯的落差：一階插叫後 15-16 點平均牌型有 3NT 可叫，二階插叫後就沒有對應叫品了。</t>
         </is>
       </c>
     </row>
